--- a/docs/АРСЕНАЛ 5.0.0 — карты целиком.xlsx
+++ b/docs/АРСЕНАЛ 5.0.0 — карты целиком.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон обломок (трофей), размести там тайл недоступной местности. Затем удали эту карту.</t>
+          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон трофей (трофей), размести там тайл недоступной местности. Затем удали эту карту.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>можешь тратить келемий вместо обломков в действии Наука</t>
+          <t>можешь тратить келемий вместо трофеев в действии Наука</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>шаг науки за монеты разово или право платить науку келемием всегда — два способа обойти нехватку обломков</t>
+          <t>шаг науки за монеты разово или право платить науку келемием всегда — два способа обойти нехватку трофеев</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>можешь тратить келемий вместо обломков в действии Наука</t>
+          <t>можешь тратить келемий вместо трофеев в действии Наука</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ: забери в трофеи чужой жетон с гекса, где стоит твоя пехота, и верни эту пехоту в свой запас</t>
+          <t>СПЕЦ: забери на место уничтоженных жетонов чужой жетон с гекса, где стоит твоя пехота, и верни эту пехоту в свой запас</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон обломок (трофей), размести там тайл недоступной местности. Затем удали эту карту.</t>
+          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон трофей (трофей), размести там тайл недоступной местности. Затем удали эту карту.</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>можешь тратить келемий вместо обломков в действии Наука</t>
+          <t>можешь тратить келемий вместо трофеев в действии Наука</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>СПЕЦ: забери в трофеи чужой жетон с гекса, где стоит твоя пехота, и верни эту пехоту в свой запас</t>
+          <t>СПЕЦ: забери на место уничтоженных жетонов чужой жетон с гекса, где стоит твоя пехота, и верни эту пехоту в свой запас</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">

--- a/docs/АРСЕНАЛ 5.0.0 — карты целиком.xlsx
+++ b/docs/АРСЕНАЛ 5.0.0 — карты целиком.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон трофей (трофей), размести там тайл недоступной местности. Затем удали эту карту.</t>
+          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон по трофею, размести там тайл недоступной местности. Затем удали эту карту.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон трофей (трофей), размести там тайл недоступной местности. Затем удали эту карту.</t>
+          <t>СПЕЦ: минус 4 боеприпаса, выбери гекс, удали все жетоны с него владельцам/в запас, возьми за каждый удалённый жетон по трофею, размести там тайл недоступной местности. Затем удали эту карту.</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
